--- a/excle/Madi.xlsx
+++ b/excle/Madi.xlsx
@@ -8,15 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC232156-25F0-4E38-B5C0-FA97F3556661}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54543FC2-9774-402B-B8CC-76F6545F4E9E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{18180E48-4F42-4510-9F57-0C3F8EAA6635}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicine" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicine!$F$3:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$F$4:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$F$3:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet4!$F$3:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet5!$E$3:$E$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
   <si>
     <t xml:space="preserve">   medicineName:{</t>
   </si>
@@ -96,45 +104,6 @@
     <t>medicineName, medicineType, medicinePrice, medicineDescription, medicineCompany, medicineImage, medicineQuantity, medicineExpiryDate, medicineManufactureDate, medicineCategory, medicineSubCategory, medicineId, medicineWtg,</t>
   </si>
   <si>
-    <t>"medicineName":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineType":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicinePrice":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineDescription":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineCompany":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineImage":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineQuantity":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineExpiryDate":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineManufactureDate":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineCategory":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineSubCategory":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineId":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "medicineWtg":</t>
-  </si>
-  <si>
     <t>{</t>
   </si>
   <si>
@@ -663,13 +632,283 @@
   </si>
   <si>
     <t>}</t>
+  </si>
+  <si>
+    <t>"name":"Abcd",</t>
+  </si>
+  <si>
+    <t>"address":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyAddress":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyDescription":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyEmail":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyId":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyLogo":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyName":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyPhone":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyPic":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyStatus":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyType":"Abcd",</t>
+  </si>
+  <si>
+    <t>"companyWebsite":"Abcd",</t>
+  </si>
+  <si>
+    <t>"dob":"Abcd",</t>
+  </si>
+  <si>
+    <t>"email":"Abcd",</t>
+  </si>
+  <si>
+    <t>"gst":"Abcd",</t>
+  </si>
+  <si>
+    <t>"password":"Abcd",</t>
+  </si>
+  <si>
+    <t>"phone":"Abcd",</t>
+  </si>
+  <si>
+    <t>"profile":"Abcd",</t>
+  </si>
+  <si>
+    <t>"role":"Abcd",</t>
+  </si>
+  <si>
+    <t>"address":"efgh",</t>
+  </si>
+  <si>
+    <t>"adharCard":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyAddress":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyDescription":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyEmail":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyId":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyLogo":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyName":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyPhone":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyPic":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyStatus":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyType":"efgh",</t>
+  </si>
+  <si>
+    <t>"companyWebsite":"efgh",</t>
+  </si>
+  <si>
+    <t>"dob":"efgh",</t>
+  </si>
+  <si>
+    <t>"email":"efgh",</t>
+  </si>
+  <si>
+    <t>"gst":"efgh",</t>
+  </si>
+  <si>
+    <t>"id":"efgh",</t>
+  </si>
+  <si>
+    <t>"panCard":"efgh",</t>
+  </si>
+  <si>
+    <t>"password":"efgh",</t>
+  </si>
+  <si>
+    <t>"phone":"efgh",</t>
+  </si>
+  <si>
+    <t>"profile":"efgh",</t>
+  </si>
+  <si>
+    <t>"referenc":"efgh",</t>
+  </si>
+  <si>
+    <t>"role":"efgh",</t>
+  </si>
+  <si>
+    <t>"name":"efgh",</t>
+  </si>
+  <si>
+    <t>"email:</t>
+  </si>
+  <si>
+    <t>"name":"Inve",</t>
+  </si>
+  <si>
+    <t>"address":"Inve",</t>
+  </si>
+  <si>
+    <t>"companyName":"Inve",</t>
+  </si>
+  <si>
+    <t>"dob":"Inve",</t>
+  </si>
+  <si>
+    <t>"email":"Inve",</t>
+  </si>
+  <si>
+    <t>"id":"Inve",</t>
+  </si>
+  <si>
+    <t>"password":"Inve",</t>
+  </si>
+  <si>
+    <t>"phone":"Inve",</t>
+  </si>
+  <si>
+    <t>"profile":"Inve",</t>
+  </si>
+  <si>
+    <t>"role":"Inve",</t>
+  </si>
+  <si>
+    <t>"name":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"address":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"companyName":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"dob":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"email":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"id":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"password":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"phone":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"profile":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"mail":"Inv auth",</t>
+  </si>
+  <si>
+    <t>"role":"Inv auth"</t>
+  </si>
+  <si>
+    <t>address,</t>
+  </si>
+  <si>
+    <t>companyName,</t>
+  </si>
+  <si>
+    <t>dob,</t>
+  </si>
+  <si>
+    <t>email,</t>
+  </si>
+  <si>
+    <t>id,</t>
+  </si>
+  <si>
+    <t>mail:</t>
+  </si>
+  <si>
+    <t>password,</t>
+  </si>
+  <si>
+    <t>phone,</t>
+  </si>
+  <si>
+    <t>profile,</t>
+  </si>
+  <si>
+    <t>role,</t>
+  </si>
+  <si>
+    <t>name,</t>
+  </si>
+  <si>
+    <t>"medicineName":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineType":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicinePrice":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineDescription":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineCompany":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineImage":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineQuantity":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineExpiryDate":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineManufactureDate":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineCategory":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineSubCategory":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineId":"med1",</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "medicineWtg":"med1",</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,6 +944,13 @@
       <sz val="9"/>
       <color rgb="FFB5CEA8"/>
       <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -749,7 +995,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -759,6 +1005,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1349,21 +1598,21 @@
     </row>
     <row r="59" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="G59" t="str">
         <f>+F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71</f>
-        <v>"medicineName": "medicineType": "medicinePrice": "medicineDescription": "medicineCompany": "medicineImage": "medicineQuantity": "medicineExpiryDate": "medicineManufactureDate": "medicineCategory": "medicineSubCategory": "medicineId": "medicineWtg":</v>
+        <v>"medicineName":"med1", "medicineType":"med1", "medicinePrice":"med1", "medicineDescription":"med1", "medicineCompany":"med1", "medicineImage":"med1", "medicineQuantity":"med1", "medicineExpiryDate":"med1", "medicineManufactureDate":"med1", "medicineCategory":"med1", "medicineSubCategory":"med1", "medicineId":"med1", "medicineWtg":"med1",</v>
       </c>
     </row>
     <row r="60" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="G61" t="s">
         <v>21</v>
@@ -1371,122 +1620,122 @@
     </row>
     <row r="62" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F64" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F69" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F70" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F71" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F73" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F74" s="3" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F75" s="3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F76" s="3" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F77" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F78" s="3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F79" s="3" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F80" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F81" s="3" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F82" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F83" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F84" s="3" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F85" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F86" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="6:6" x14ac:dyDescent="0.25">
@@ -1494,7 +1743,7 @@
     </row>
     <row r="88" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F88" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1519,4 +1768,461 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7091C48-59BB-4491-BADF-82A608EBDEFE}">
+  <dimension ref="F4:F24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F21" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922EAF34-FC0F-4E58-85FD-80AA6A482844}">
+  <dimension ref="F3:F26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F21" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F25" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="F3:F26" xr:uid="{DE75AC39-C7DA-45F4-BACC-C14CDB329EB4}">
+    <sortState ref="F4:F26">
+      <sortCondition ref="F3:F26"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72EE982-E1B7-472E-8387-1E2DC6EEED05}">
+  <dimension ref="F3:F13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="41.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="F3:F13" xr:uid="{7FCC2090-97E3-4735-A191-1A8392F4AF9A}">
+    <sortState ref="F4:F13">
+      <sortCondition ref="F3:F13"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B0651C-BE2A-4DE7-928E-ABB1AB7C7672}">
+  <dimension ref="E3:I18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" t="str">
+        <f>+F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13</f>
+        <v>name,address,companyName,dob,email,id,mail:password,phone,profile,role,</v>
+      </c>
+    </row>
+    <row r="4" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="I14" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="I16" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I17" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I18" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/excle/Madi.xlsx
+++ b/excle/Madi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91908\Desktop\MediScripts\MediScrpts-BD\excle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54543FC2-9774-402B-B8CC-76F6545F4E9E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C575B24-6570-494C-9870-16D0FC9F75C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{18180E48-4F42-4510-9F57-0C3F8EAA6635}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" activeTab="6" xr2:uid="{18180E48-4F42-4510-9F57-0C3F8EAA6635}"/>
   </bookViews>
   <sheets>
     <sheet name="Medicine" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Admin" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Admin!$A$3:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Medicine!$F$3:$F$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$F$4:$F$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$F$3:$F$26</definedName>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t xml:space="preserve">   medicineName:{</t>
   </si>
@@ -902,6 +905,84 @@
   </si>
   <si>
     <t xml:space="preserve"> "medicineWtg":"med1",</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>companyAddress</t>
+  </si>
+  <si>
+    <t>companyEmail</t>
+  </si>
+  <si>
+    <t>companyName</t>
+  </si>
+  <si>
+    <t>companyPhone</t>
+  </si>
+  <si>
+    <t>companyWebsite</t>
+  </si>
+  <si>
+    <t>dob</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>gst</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'name' ,type:"text" ,placeholder:"Enter Name"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'dob' ,type:"date" ,placeholder:"Enter DOB"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'phone' ,type:"number" ,placeholder:"Enter Phone"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'email' ,type:"email" ,placeholder:"Enter Email"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'address' ,type:"text" ,placeholder:"Enter Address"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'companyName' ,type:"text" ,placeholder:"Enter CompanyName"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'companyPhone' ,type:"number" ,placeholder:"Enter CompanyPhone"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'Companymail' ,type:"email" ,placeholder:"Enter CompanyEmail"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'companyAddress' ,type:"text" ,placeholder:"Enter CompanyAddress"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'gst' ,type:"text" ,placeholder:"Enter GST NO"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'website' ,type:"text" ,placeholder:"Enter CompanyWebsite"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'password' ,type:"text" ,placeholder:"Enter Password"  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                {name:'password' ,type:"text" ,placeholder:"Enter Conform Password"  }</t>
   </si>
 </sst>
 </file>
@@ -2225,4 +2306,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30E59188-C084-4D33-B79F-F60C663F67E5}">
+  <dimension ref="A3:D15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" t="str">
+        <f>+"&lt;input name='name' type="&amp;"text"&amp;" placeholder="&amp;"Enter "&amp;A3&amp;" className="&amp;"border p-2 rounded"&amp;" /&gt;"</f>
+        <v>&lt;input name='name' type=text placeholder=Enter name className=border p-2 rounded /&gt;</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:A14" xr:uid="{74DB734A-D6D0-42F7-90F4-FE6CFCF36E0A}">
+    <sortState ref="A4:A14">
+      <sortCondition ref="A3:A14"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10138A6-5160-46EF-89B1-7B459174E72A}">
+  <dimension ref="G5:G18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="117.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>